--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6143-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6143-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CDE938A-BD66-45C6-A74C-1B285D6A68F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CE6F3D3-D208-423D-A88E-F79AACA6E27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{A2F314FC-AD6C-4E87-833B-416844133096}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{35F1B96F-4349-4748-847E-F30B0F53950E}"/>
   </bookViews>
   <sheets>
     <sheet name="6143-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1481,27 +1481,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448225E7-664F-4C63-88EC-FE2CD17E9725}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6C2233A-0CE8-41B2-AD90-E5042B50DF4D}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1535,7 +1534,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1571,7 +1570,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1623,7 +1622,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1691,7 +1690,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1763,7 +1762,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1835,7 +1834,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1907,7 +1906,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1979,7 +1978,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2051,7 +2050,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2123,7 +2122,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2195,7 +2194,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2267,7 +2266,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2411,7 +2410,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2483,7 +2482,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2555,7 +2554,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2627,7 +2626,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2699,7 +2698,7 @@
         <v>8.85</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2771,7 +2770,7 @@
         <v>8.32</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2843,7 +2842,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2915,7 +2914,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2987,7 +2986,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3059,7 +3058,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3131,7 +3130,7 @@
         <v>6.65</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3203,7 +3202,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3275,7 +3274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3347,7 +3346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3419,7 +3418,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3491,7 +3490,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3563,7 +3562,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3635,7 +3634,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36" t="s">
         <v>52</v>
       </c>
